--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202608/Currency_P&L_20260811.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202608/Currency_P&L_20260811.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -44,6 +44,30 @@
   </si>
   <si>
     <t>United States Return</t>
+  </si>
+  <si>
+    <t>United Kingdom MTM</t>
+  </si>
+  <si>
+    <t>United Kingdom Return</t>
+  </si>
+  <si>
+    <t>South Korea MTM</t>
+  </si>
+  <si>
+    <t>South Korea Return</t>
+  </si>
+  <si>
+    <t>Taiwan MTM</t>
+  </si>
+  <si>
+    <t>Taiwan Return</t>
+  </si>
+  <si>
+    <t>KRX MTM</t>
+  </si>
+  <si>
+    <t>KRX Return</t>
   </si>
 </sst>
 </file>
@@ -405,10 +429,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,8 +463,32 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="2">
         <v>46176</v>
       </c>
@@ -472,7 +520,7 @@
         <v>-0.002062</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:18">
       <c r="A3" s="2">
         <v>46177</v>
       </c>
@@ -504,7 +552,7 @@
         <v>-0.01325</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:18">
       <c r="A4" s="2">
         <v>46178</v>
       </c>
@@ -536,7 +584,7 @@
         <v>-0.057191</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>46181</v>
       </c>
@@ -568,7 +616,7 @@
         <v>0.013874</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>46182</v>
       </c>
@@ -600,7 +648,7 @@
         <v>-0.00732</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>46183</v>
       </c>
@@ -632,7 +680,7 @@
         <v>-0.013745</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>46184</v>
       </c>
@@ -664,7 +712,7 @@
         <v>0.027766</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>46185</v>
       </c>
@@ -696,7 +744,7 @@
         <v>0.001551</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>46188</v>
       </c>
@@ -728,7 +776,7 @@
         <v>0.015633</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:18">
       <c r="A11" s="2">
         <v>46189</v>
       </c>
@@ -760,7 +808,7 @@
         <v>-0.009766</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:18">
       <c r="A12" s="2">
         <v>46190</v>
       </c>
@@ -792,7 +840,7 @@
         <v>-0.00462</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:18">
       <c r="A13" s="2">
         <v>46191</v>
       </c>
@@ -824,7 +872,7 @@
         <v>0.002327</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:18">
       <c r="A14" s="2">
         <v>46195</v>
       </c>
@@ -856,7 +904,7 @@
         <v>-0.000175</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:18">
       <c r="A15" s="2">
         <v>46196</v>
       </c>
@@ -888,7 +936,7 @@
         <v>-0.020594</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:18">
       <c r="A16" s="2">
         <v>46197</v>
       </c>
@@ -1432,7 +1480,7 @@
         <v>-0.017473</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:16">
       <c r="A33" s="2">
         <v>46223</v>
       </c>
@@ -1464,7 +1512,7 @@
         <v>0.001085</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:16">
       <c r="A34" s="2">
         <v>46224</v>
       </c>
@@ -1496,7 +1544,7 @@
         <v>0.034142</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:16">
       <c r="A35" s="2">
         <v>46225</v>
       </c>
@@ -1528,7 +1576,7 @@
         <v>-0.000831</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:16">
       <c r="A36" s="2">
         <v>46226</v>
       </c>
@@ -1560,7 +1608,7 @@
         <v>-0.009573999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:16">
       <c r="A37" s="2">
         <v>46227</v>
       </c>
@@ -1592,7 +1640,7 @@
         <v>-0.013868</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:16">
       <c r="A38" s="2">
         <v>46230</v>
       </c>
@@ -1624,7 +1672,7 @@
         <v>-0.007622</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:16">
       <c r="A39" s="2">
         <v>46231</v>
       </c>
@@ -1656,7 +1704,7 @@
         <v>-0.014188</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:16">
       <c r="A40" s="2">
         <v>46232</v>
       </c>
@@ -1688,12 +1736,12 @@
         <v>-0.021684</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:16">
       <c r="A41" s="2">
         <v>46233</v>
       </c>
       <c r="B41">
-        <v>85859219.67</v>
+        <v>87859219.67</v>
       </c>
       <c r="C41">
         <v>30846.08</v>
@@ -1720,216 +1768,300 @@
         <v>0.029989</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:16">
       <c r="A42" s="2">
         <v>46234</v>
       </c>
       <c r="B42">
-        <v>86263492.97</v>
+        <v>88263665.98999999</v>
       </c>
       <c r="C42">
         <v>-19784.59</v>
       </c>
       <c r="D42">
-        <v>-0.00023</v>
+        <v>-0.000225</v>
       </c>
       <c r="E42">
         <v>68001.59</v>
       </c>
       <c r="F42">
-        <v>0.000792</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="G42">
         <v>-63561.88</v>
       </c>
       <c r="H42">
-        <v>-0.00074</v>
+        <v>-0.000723</v>
       </c>
       <c r="I42">
         <v>434413.15</v>
       </c>
       <c r="J42">
-        <v>0.00506</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>0.004944</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" s="2">
         <v>46237</v>
       </c>
       <c r="B43">
-        <v>87113767.19</v>
+        <v>89113874.08</v>
       </c>
       <c r="C43">
-        <v>223.1</v>
+        <v>-1413.2</v>
       </c>
       <c r="D43">
-        <v>3E-06</v>
+        <v>-1.6E-05</v>
       </c>
       <c r="E43">
         <v>-42459.98</v>
       </c>
       <c r="F43">
-        <v>-0.000492</v>
+        <v>-0.000481</v>
       </c>
       <c r="G43">
-        <v>-44160.69</v>
+        <v>-45582.27</v>
       </c>
       <c r="H43">
-        <v>-0.000512</v>
+        <v>-0.000516</v>
       </c>
       <c r="I43">
-        <v>897212.4300000001</v>
+        <v>897264.64</v>
       </c>
       <c r="J43">
-        <v>0.010401</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>0.010166</v>
+      </c>
+      <c r="K43">
+        <v>19.3</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>2401.18</v>
+      </c>
+      <c r="N43">
+        <v>2.7E-05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" s="2">
         <v>46238</v>
       </c>
       <c r="B44">
-        <v>91262886.70999999</v>
+        <v>93267004.43000001</v>
       </c>
       <c r="C44">
-        <v>-36054.21</v>
+        <v>-49988.29</v>
       </c>
       <c r="D44">
-        <v>-0.000414</v>
+        <v>-0.000561</v>
       </c>
       <c r="E44">
         <v>15569.32</v>
       </c>
       <c r="F44">
-        <v>0.000179</v>
+        <v>0.000175</v>
       </c>
       <c r="G44">
-        <v>38138.16</v>
+        <v>37596.13</v>
       </c>
       <c r="H44">
-        <v>0.000438</v>
+        <v>0.000422</v>
       </c>
       <c r="I44">
-        <v>4150722.13</v>
+        <v>4149005.76</v>
       </c>
       <c r="J44">
-        <v>0.047647</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>0.046558</v>
+      </c>
+      <c r="K44">
+        <v>-29.38</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>23429.3</v>
+      </c>
+      <c r="N44">
+        <v>0.000263</v>
+      </c>
+      <c r="O44">
+        <v>-3568.85</v>
+      </c>
+      <c r="P44">
+        <v>-4E-05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" s="2">
         <v>46239</v>
       </c>
       <c r="B45">
-        <v>90306025.06999999</v>
+        <v>92301723.41</v>
       </c>
       <c r="C45">
-        <v>25387</v>
+        <v>21264.82</v>
       </c>
       <c r="D45">
-        <v>0.000278</v>
+        <v>0.000228</v>
       </c>
       <c r="E45">
-        <v>86138.85000000001</v>
+        <v>88335.56</v>
       </c>
       <c r="F45">
-        <v>0.000944</v>
+        <v>0.000947</v>
       </c>
       <c r="G45">
-        <v>-39467.47</v>
+        <v>-41322.82</v>
       </c>
       <c r="H45">
-        <v>-0.000432</v>
+        <v>-0.000443</v>
       </c>
       <c r="I45">
-        <v>-1008525.76</v>
+        <v>-1012562.54</v>
       </c>
       <c r="J45">
-        <v>-0.011051</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>-0.010857</v>
+      </c>
+      <c r="K45">
+        <v>-14.36</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>-471.78</v>
+      </c>
+      <c r="N45">
+        <v>-5E-06</v>
+      </c>
+      <c r="O45">
+        <v>-241.2</v>
+      </c>
+      <c r="P45">
+        <v>-3E-06</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" s="2">
         <v>46240</v>
       </c>
       <c r="B46">
-        <v>90022498.70999999</v>
+        <v>92036435.27</v>
       </c>
       <c r="C46">
-        <v>-41829.03</v>
+        <v>-53377</v>
       </c>
       <c r="D46">
-        <v>-0.000463</v>
+        <v>-0.000578</v>
       </c>
       <c r="E46">
-        <v>492.23</v>
+        <v>3855.83</v>
       </c>
       <c r="F46">
-        <v>5E-06</v>
+        <v>4.2E-05</v>
       </c>
       <c r="G46">
-        <v>69978.08</v>
+        <v>75231.19</v>
       </c>
       <c r="H46">
-        <v>0.000775</v>
+        <v>0.000815</v>
       </c>
       <c r="I46">
-        <v>-193940.2</v>
+        <v>-192898.88</v>
       </c>
       <c r="J46">
-        <v>-0.002148</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>-0.00209</v>
+      </c>
+      <c r="K46">
+        <v>12.07</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>21137.95</v>
+      </c>
+      <c r="N46">
+        <v>0.000229</v>
+      </c>
+      <c r="O46">
+        <v>-1103.88</v>
+      </c>
+      <c r="P46">
+        <v>-1.2E-05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" s="2">
         <v>46241</v>
       </c>
       <c r="B47">
-        <v>90981739.18000001</v>
+        <v>92992013.92</v>
       </c>
       <c r="C47">
-        <v>-1823.07</v>
+        <v>-4073.83</v>
       </c>
       <c r="D47">
-        <v>-2E-05</v>
+        <v>-4.4E-05</v>
       </c>
       <c r="E47">
-        <v>-20646.93</v>
+        <v>-19457.99</v>
       </c>
       <c r="F47">
-        <v>-0.000229</v>
+        <v>-0.000211</v>
       </c>
       <c r="G47">
-        <v>-23455.47</v>
+        <v>-18144.01</v>
       </c>
       <c r="H47">
-        <v>-0.000261</v>
+        <v>-0.000197</v>
       </c>
       <c r="I47">
-        <v>1025543.53</v>
+        <v>1024969.29</v>
       </c>
       <c r="J47">
-        <v>0.011392</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>0.011137</v>
+      </c>
+      <c r="K47">
+        <v>-15.98</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>-8668.379999999999</v>
+      </c>
+      <c r="N47">
+        <v>-9.399999999999999E-05</v>
+      </c>
+      <c r="O47">
+        <v>928.17</v>
+      </c>
+      <c r="P47">
+        <v>1E-05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" s="2">
         <v>46244</v>
       </c>
       <c r="B48">
-        <v>91383338.53</v>
+        <v>93396729.11</v>
       </c>
       <c r="C48">
-        <v>43163.32</v>
+        <v>41857</v>
       </c>
       <c r="D48">
-        <v>0.000474</v>
+        <v>0.00045</v>
       </c>
       <c r="E48">
-        <v>10959.82</v>
+        <v>12045.39</v>
       </c>
       <c r="F48">
-        <v>0.00012</v>
+        <v>0.00013</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -1938,24 +2070,42 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>408931.77</v>
+        <v>411964.27</v>
       </c>
       <c r="J48">
-        <v>0.004495</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>0.00443</v>
+      </c>
+      <c r="K48">
+        <v>-18.62</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>1087.85</v>
+      </c>
+      <c r="N48">
+        <v>1.2E-05</v>
+      </c>
+      <c r="O48">
+        <v>351.8</v>
+      </c>
+      <c r="P48">
+        <v>4E-06</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49" s="2">
         <v>46245</v>
       </c>
       <c r="B49">
-        <v>91143582.97</v>
+        <v>93127098.19</v>
       </c>
       <c r="C49">
-        <v>-47652.9</v>
+        <v>-52582.27</v>
       </c>
       <c r="D49">
-        <v>-0.000521</v>
+        <v>-0.000563</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1964,16 +2114,40 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>-65470.49</v>
+        <v>-65031.04</v>
       </c>
       <c r="H49">
-        <v>-0.0007159999999999999</v>
+        <v>-0.000696</v>
       </c>
       <c r="I49">
-        <v>-105805.98</v>
+        <v>-109712.91</v>
       </c>
       <c r="J49">
-        <v>-0.001158</v>
+        <v>-0.001175</v>
+      </c>
+      <c r="K49">
+        <v>-112.74</v>
+      </c>
+      <c r="L49">
+        <v>-1E-06</v>
+      </c>
+      <c r="M49">
+        <v>-16656.67</v>
+      </c>
+      <c r="N49">
+        <v>-0.000178</v>
+      </c>
+      <c r="O49">
+        <v>-2819.35</v>
+      </c>
+      <c r="P49">
+        <v>-3E-05</v>
+      </c>
+      <c r="Q49">
+        <v>-2055.05</v>
+      </c>
+      <c r="R49">
+        <v>-2.2E-05</v>
       </c>
     </row>
   </sheetData>
